--- a/human_resources_forms/013_employee_benefits_assessment_form--human_resources_forms.xlsx
+++ b/human_resources_forms/013_employee_benefits_assessment_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Employee Benefits</t>
+          <t>Job Satisfaction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>employee_benefits_form_2</t>
+          <t>job_benefits_packages</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Benefits Packages</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>commute_options</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Commute Options</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>employee_benefits_form_3</t>
+          <t>work_environment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Job Satisfaction</t>
+          <t>Work Environment</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>employee_benefits_form_4</t>
+          <t>team_dynamics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Job Satisfaction</t>
+          <t>Team Dynamics</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>job_satisfaction</t>
+          <t>company_culture</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Job Satisfaction</t>
+          <t>Company Culture</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>employee_benefits_form_5</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Benefits Packages</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>employee_benefits_form_6</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Benefits Packages</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,40 +699,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>benefits_packages</t>
+          <t>job_satisfaction</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Benefits Packages</t>
+          <t>Job Satisfaction (2)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>employee_benefits_form_7</t>
+          <t>benefits_packages_satisfaction</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Commute Options</t>
+          <t>Benefits Packages Satisfaction</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>commute_options</t>
+          <t>commute_improvement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Commute Options</t>
+          <t>Commute Improvement</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,338 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>employee_benefits_form_8</t>
+          <t>job_value_alignment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Work Environment</t>
+          <t>Job Value Alignment</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>work_environment</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Work Environment</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_9</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Team Dynamics</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>team_dynamics</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>prophets</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>prophets</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>prophets</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Company Culture</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>company_culture</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Company Culture</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_11</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>management</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>prophets</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>prophets</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>prophets</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_12</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>prophets</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_13</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Employee Benefits Assessment</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_14</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Employee Benefits Assessment</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1121,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1154,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1171,121 +849,121 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>employee_benefits_form_3_choices</t>
+          <t>job_benefits_packages_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>employee_benefits_form_3_choices</t>
+          <t>job_benefits_packages_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>employee_benefits_form_4_choices</t>
+          <t>commute_options_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>employee_benefits_form_4_choices</t>
+          <t>commute_options_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>work_environment_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>work_environment_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>employee_benefits_form_5_choices</t>
+          <t>team_dynamics_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1302,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>employee_benefits_form_5_choices</t>
+          <t>team_dynamics_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1319,7 +997,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>employee_benefits_form_6_choices</t>
+          <t>company_culture_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1336,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>employee_benefits_form_6_choices</t>
+          <t>company_culture_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1353,7 +1031,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>benefits_packages_choices</t>
+          <t>management_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1370,7 +1048,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>benefits_packages_choices</t>
+          <t>management_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1387,7 +1065,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>employee_benefits_form_7_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1404,7 +1082,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>employee_benefits_form_7_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1421,41 +1099,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>commute_options_choices</t>
+          <t>benefits_packages_satisfaction_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>commute_options_choices</t>
+          <t>benefits_packages_satisfaction_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>employee_benefits_form_8_choices</t>
+          <t>commute_improvement_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1472,7 +1150,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>employee_benefits_form_8_choices</t>
+          <t>commute_improvement_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1489,7 +1167,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>work_environment_choices</t>
+          <t>job_value_alignment_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1506,7 +1184,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>work_environment_choices</t>
+          <t>job_value_alignment_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1515,312 +1193,6 @@
         </is>
       </c>
       <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_9_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_9_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_10_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_10_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>company_culture_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>company_culture_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_11_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_11_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_12_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_12_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>prophets_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>prophets_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>communication_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>communication_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_13_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_13_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_14_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>employee_benefits_form_14_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
